--- a/Timings.xlsx
+++ b/Timings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\TESTS\gs\avis-gaussian-splatting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD597B57-E41B-4866-B8E4-70401EEEB69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC5263D-1852-4E04-B4C2-5A4C99A2767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5970" yWindow="1935" windowWidth="30795" windowHeight="15975" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
+    <workbookView xWindow="2610" yWindow="1470" windowWidth="22395" windowHeight="18285" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>16.06.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>Nr Of Points</t>
   </si>
@@ -50,22 +44,64 @@
     <t>Training Duration</t>
   </si>
   <si>
-    <t>PSNR</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Smart Initialization (DICOM-Colors)</t>
-  </si>
-  <si>
     <t>Resolution</t>
   </si>
   <si>
     <t>half</t>
   </si>
   <si>
-    <t>Loss</t>
+    <t>Smart Initialization</t>
+  </si>
+  <si>
+    <t>Random Initialization</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>17.06.</t>
+  </si>
+  <si>
+    <t>PSNR (Start)</t>
+  </si>
+  <si>
+    <t>Loss (Start)</t>
+  </si>
+  <si>
+    <t>Loss (End)</t>
+  </si>
+  <si>
+    <t>PSNR (End)</t>
+  </si>
+  <si>
+    <t>With Orientation, DICOM Colors</t>
+  </si>
+  <si>
+    <t>Without orientation, DICOM colors</t>
+  </si>
+  <si>
+    <t>WO Orientation, random Colors</t>
+  </si>
+  <si>
+    <t>W Orientation, random Colors</t>
+  </si>
+  <si>
+    <t>Bad Placement</t>
+  </si>
+  <si>
+    <t>Better Placement</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>b3594496-d</t>
+  </si>
+  <si>
+    <t>bb28143d-9</t>
+  </si>
+  <si>
+    <t>35445b03-3</t>
   </si>
 </sst>
 </file>
@@ -73,9 +109,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,16 +119,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -100,20 +159,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
     </dxf>
@@ -131,16 +223,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}" name="Tabelle1" displayName="Tabelle1" ref="C7:I21" totalsRowShown="0">
-  <autoFilter ref="C7:I21" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA3F6830-BAC4-4FD9-A394-9E999F8033CE}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{F091966C-55EF-48D3-B415-C56E9FE9AAC5}" name="Method"/>
-    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Training Duration" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{E9B572CD-3E9A-4CEA-9B7C-305488712FFB}" name="Nr Of Points"/>
-    <tableColumn id="5" xr3:uid="{F7B34D60-0824-4BD2-B654-A34383077C04}" name="PSNR"/>
-    <tableColumn id="6" xr3:uid="{94FB43B6-19FB-4A94-A78E-1026CB6E37F2}" name="Resolution"/>
-    <tableColumn id="7" xr3:uid="{3B9F1CBC-2959-4830-89AB-95327E9D0F3B}" name="Loss"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}" name="Tabelle1" displayName="Tabelle1" ref="C7:J21" totalsRowShown="0">
+  <autoFilter ref="C7:J21" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{EA3F6830-BAC4-4FD9-A394-9E999F8033CE}" name="Code"/>
+    <tableColumn id="2" xr3:uid="{F091966C-55EF-48D3-B415-C56E9FE9AAC5}" name="Training Duration"/>
+    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Nr Of Points" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{E9B572CD-3E9A-4CEA-9B7C-305488712FFB}" name="Resolution"/>
+    <tableColumn id="6" xr3:uid="{94FB43B6-19FB-4A94-A78E-1026CB6E37F2}" name="PSNR (Start)"/>
+    <tableColumn id="7" xr3:uid="{18CF464E-7E9E-4DB2-BCF0-CFB02527AC18}" name="PSNR (End)"/>
+    <tableColumn id="8" xr3:uid="{FDB7CFA4-5E00-479A-ADF7-E103BC1ED88C}" name="Loss (Start)"/>
+    <tableColumn id="9" xr3:uid="{B4B56141-5A8A-475C-ADE3-FD142F451865}" name="Loss (End)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}" name="Tabelle13" displayName="Tabelle13" ref="C26:K40" totalsRowShown="0">
+  <autoFilter ref="C26:K40" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{5ADD7675-23D6-40D9-8031-52023CB23480}" name="Code"/>
+    <tableColumn id="2" xr3:uid="{14203E69-6608-483D-BBEB-EB038E259A23}" name="Training Duration"/>
+    <tableColumn id="3" xr3:uid="{5FE5403A-FE12-41A1-BE7D-0FC20267D7C4}" name="Nr Of Points" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{6BB98B40-3C2F-4659-B95E-6F199432AF52}" name="Resolution"/>
+    <tableColumn id="5" xr3:uid="{B4B69CDA-51CC-4214-89F5-CD30E8EB4931}" name="PSNR (Start)"/>
+    <tableColumn id="6" xr3:uid="{C2AAF3AF-1964-4907-9B53-4AAEF160B32B}" name="PSNR (End)"/>
+    <tableColumn id="7" xr3:uid="{33CAF3C7-8F0F-42A6-A2D8-A3625FCD81F9}" name="Loss (Start)"/>
+    <tableColumn id="8" xr3:uid="{5A2CABB3-9FD4-4659-A472-928036ED601F}" name="Loss (End)"/>
+    <tableColumn id="9" xr3:uid="{845B5EE9-5F9F-4A7C-AF02-F0D943496E19}" name="Comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -463,104 +574,340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C03B34-FF9A-4BAB-BFFD-D449B574B7AC}">
-  <dimension ref="C7:I21"/>
+  <dimension ref="C5:K40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
       </c>
       <c r="F7" t="s">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="E8">
+        <v>100000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>26.5</v>
+      </c>
+      <c r="H8">
+        <v>30.5</v>
+      </c>
+      <c r="I8">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="J8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="E9">
+        <v>100000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>26.65</v>
+      </c>
+      <c r="H9">
+        <v>30.7</v>
+      </c>
+      <c r="I9">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="J9">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.21319444444444444</v>
+      </c>
+      <c r="E10">
+        <v>100000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>30.29</v>
+      </c>
+      <c r="H10">
+        <v>34.6</v>
+      </c>
+      <c r="I10">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J10">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.21319444444444444</v>
+      </c>
+      <c r="E11">
+        <v>100000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>30.35</v>
+      </c>
+      <c r="H11">
+        <v>35.1</v>
+      </c>
+      <c r="I11">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J11">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E16" s="1"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E17" s="1"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E20" s="1"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E21" s="1"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E26" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="3">
-        <v>3.8194444444444443E-3</v>
-      </c>
-      <c r="F8">
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="E27" s="4">
         <v>100000</v>
       </c>
-      <c r="G8">
-        <v>32.65</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>9.9500000000000005E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="1"/>
+      <c r="F27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>26.81</v>
+      </c>
+      <c r="H27">
+        <v>30.76</v>
+      </c>
+      <c r="I27">
+        <v>1.9E-2</v>
+      </c>
+      <c r="J27">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.26319444444444445</v>
+      </c>
+      <c r="E28" s="4">
+        <v>100000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>25.88</v>
+      </c>
+      <c r="H28">
+        <v>30.01</v>
+      </c>
+      <c r="I28">
+        <v>1.47E-2</v>
+      </c>
+      <c r="J28">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Timings.xlsx
+++ b/Timings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\TESTS\gs\avis-gaussian-splatting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC5263D-1852-4E04-B4C2-5A4C99A2767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723323E2-75A2-4090-AD74-D10E792BDEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1470" windowWidth="22395" windowHeight="18285" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
+    <workbookView xWindow="5805" yWindow="1500" windowWidth="35625" windowHeight="17385" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
   <si>
     <t>Nr Of Points</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Resolution</t>
   </si>
   <si>
-    <t>half</t>
-  </si>
-  <si>
     <t>Smart Initialization</t>
   </si>
   <si>
@@ -95,13 +92,100 @@
     <t>Code</t>
   </si>
   <si>
-    <t>b3594496-d</t>
-  </si>
-  <si>
     <t>bb28143d-9</t>
   </si>
   <si>
     <t>35445b03-3</t>
+  </si>
+  <si>
+    <t>Nr of Points End</t>
+  </si>
+  <si>
+    <t>e7e980d1-d</t>
+  </si>
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Smart</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Training Duration (s)</t>
+  </si>
+  <si>
+    <t>561feaa9-6</t>
+  </si>
+  <si>
+    <t>FULL DATASET</t>
+  </si>
+  <si>
+    <t>ffed025f-1</t>
+  </si>
+  <si>
+    <t>FULL DATASET, wo orientation</t>
+  </si>
+  <si>
+    <t>0ab49491-5</t>
+  </si>
+  <si>
+    <t>Start=</t>
+  </si>
+  <si>
+    <t>100% Resolution =</t>
+  </si>
+  <si>
+    <t>1024x1024</t>
+  </si>
+  <si>
+    <t>4c87e4ce-9</t>
+  </si>
+  <si>
+    <t>86c60d41-2</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t>PSNR</t>
+  </si>
+  <si>
+    <t>Training Dur.</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Spalte1</t>
+  </si>
+  <si>
+    <t>Cinematic Gaussians</t>
+  </si>
+  <si>
+    <t>Gaussian Splatting</t>
+  </si>
+  <si>
+    <t>23% Training (Iteration 7000)</t>
+  </si>
+  <si>
+    <t>25.06:17:00</t>
+  </si>
+  <si>
+    <t>100k</t>
+  </si>
+  <si>
+    <t>26.06:09:00</t>
+  </si>
+  <si>
+    <t>Ohne Rotation &amp; Scaling!</t>
   </si>
 </sst>
 </file>
@@ -111,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,8 +220,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,12 +249,56 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -184,10 +327,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -196,13 +340,154 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
     </dxf>
@@ -222,36 +507,1933 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>Vergleich PSNR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Q$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PSNR (Start)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$P$8:$P$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Random</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Smart</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$10:$Q$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>27.31</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-30DB-4540-9F03-808D8C2A7F67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$R$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PSNR (End)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$P$8:$P$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Random</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Smart</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$R$10:$R$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>30.06</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-30DB-4540-9F03-808D8C2A7F67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1148451536"/>
+        <c:axId val="1148449616"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1148451536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1148449616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1148449616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1148451536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$T$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Training Duration (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$P$8:$P$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Random</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Smart</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$T$10:$T$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>969</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>824</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B15F-426B-B905-B85F10AA01C1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1248951152"/>
+        <c:axId val="1248948752"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1248951152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248948752"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1248948752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248951152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>128586</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Diagramm 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFB76DED-04C5-79CB-9661-0A68F9008448}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>461962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>252412</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Diagramm 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FBA0F4F-3D54-1C68-E6FE-6D9F3B030963}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}" name="Tabelle1" displayName="Tabelle1" ref="C7:J21" totalsRowShown="0">
-  <autoFilter ref="C7:J21" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}" name="Tabelle1" displayName="Tabelle1" ref="C7:K21" totalsRowShown="0">
+  <autoFilter ref="C7:K21" xr:uid="{B23995EE-D1AC-4E6A-A91A-80AB79A654FE}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EA3F6830-BAC4-4FD9-A394-9E999F8033CE}" name="Code"/>
     <tableColumn id="2" xr3:uid="{F091966C-55EF-48D3-B415-C56E9FE9AAC5}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Nr Of Points" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Nr Of Points" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{E9B572CD-3E9A-4CEA-9B7C-305488712FFB}" name="Resolution"/>
     <tableColumn id="6" xr3:uid="{94FB43B6-19FB-4A94-A78E-1026CB6E37F2}" name="PSNR (Start)"/>
     <tableColumn id="7" xr3:uid="{18CF464E-7E9E-4DB2-BCF0-CFB02527AC18}" name="PSNR (End)"/>
     <tableColumn id="8" xr3:uid="{FDB7CFA4-5E00-479A-ADF7-E103BC1ED88C}" name="Loss (Start)"/>
     <tableColumn id="9" xr3:uid="{B4B56141-5A8A-475C-ADE3-FD142F451865}" name="Loss (End)"/>
+    <tableColumn id="10" xr3:uid="{85F36A5D-30EB-4D28-A49E-50FA963A7ABC}" name="Nr of Points End"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}" name="Tabelle13" displayName="Tabelle13" ref="C26:K40" totalsRowShown="0">
-  <autoFilter ref="C26:K40" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}" name="Tabelle13" displayName="Tabelle13" ref="C26:L40" totalsRowShown="0">
+  <autoFilter ref="C26:L40" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5ADD7675-23D6-40D9-8031-52023CB23480}" name="Code"/>
     <tableColumn id="2" xr3:uid="{14203E69-6608-483D-BBEB-EB038E259A23}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{5FE5403A-FE12-41A1-BE7D-0FC20267D7C4}" name="Nr Of Points" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{5FE5403A-FE12-41A1-BE7D-0FC20267D7C4}" name="Nr Of Points" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{6BB98B40-3C2F-4659-B95E-6F199432AF52}" name="Resolution"/>
     <tableColumn id="5" xr3:uid="{B4B69CDA-51CC-4214-89F5-CD30E8EB4931}" name="PSNR (Start)"/>
     <tableColumn id="6" xr3:uid="{C2AAF3AF-1964-4907-9B53-4AAEF160B32B}" name="PSNR (End)"/>
     <tableColumn id="7" xr3:uid="{33CAF3C7-8F0F-42A6-A2D8-A3625FCD81F9}" name="Loss (Start)"/>
     <tableColumn id="8" xr3:uid="{5A2CABB3-9FD4-4659-A472-928036ED601F}" name="Loss (End)"/>
-    <tableColumn id="9" xr3:uid="{845B5EE9-5F9F-4A7C-AF02-F0D943496E19}" name="Comments"/>
+    <tableColumn id="9" xr3:uid="{845B5EE9-5F9F-4A7C-AF02-F0D943496E19}" name="Nr of Points End"/>
+    <tableColumn id="10" xr3:uid="{90CFA1D6-50D2-45A3-8D39-22F80E499D45}" name="Comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CAF6CA38-A879-4E1D-939A-4F49F01E476B}" name="Tabelle3" displayName="Tabelle3" ref="V7:X9" totalsRowShown="0">
+  <autoFilter ref="V7:X9" xr:uid="{CAF6CA38-A879-4E1D-939A-4F49F01E476B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{ADF7F475-D563-4612-8AD8-71DAD1D2CE7C}" name="Spalte1"/>
+    <tableColumn id="2" xr3:uid="{8EE6E213-7A6E-49E0-8C89-CA05EE60D19B}" name="Blue" dataDxfId="5" dataCellStyle="Prozent">
+      <calculatedColumnFormula>R9/R8</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{696629D8-E2FE-486F-8554-54A0C09074BE}" name="Red" dataDxfId="4" dataCellStyle="Prozent">
+      <calculatedColumnFormula>T10/T9</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24567F50-1684-4737-947B-346844D16070}" name="Tabelle15" displayName="Tabelle15" ref="C48:K62" totalsRowShown="0">
+  <autoFilter ref="C48:K62" xr:uid="{24567F50-1684-4737-947B-346844D16070}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{16B84E3B-6F04-4493-8D97-29CD2344449A}" name="Code"/>
+    <tableColumn id="2" xr3:uid="{610A843A-B98C-47B1-A6D3-CDB811A53CE8}" name="Training Duration"/>
+    <tableColumn id="3" xr3:uid="{DF755203-AFBC-4860-BD4F-4432648FEE7D}" name="Nr Of Points" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9547ACFC-FF01-4E72-884B-AF7F5B534A68}" name="Resolution"/>
+    <tableColumn id="6" xr3:uid="{F05F4F04-CECB-4BD0-9A43-9A1B85591A96}" name="PSNR (Start)"/>
+    <tableColumn id="7" xr3:uid="{B62AC83F-DE2B-468B-B129-6BD01F2C00B2}" name="PSNR (End)"/>
+    <tableColumn id="8" xr3:uid="{4028D52E-B5DA-47A7-B3BD-0D4D94C724A6}" name="Loss (Start)"/>
+    <tableColumn id="9" xr3:uid="{DBF42164-BA6E-4D04-BF36-57D87074E573}" name="Loss (End)"/>
+    <tableColumn id="10" xr3:uid="{D5E791A1-F987-4E40-B829-4893B9F2EB70}" name="Nr of Points End"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}" name="Tabelle136" displayName="Tabelle136" ref="C67:L81" totalsRowShown="0">
+  <autoFilter ref="C67:L81" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{42E5749D-01BF-4157-AA2C-7D3D72631E67}" name="Code"/>
+    <tableColumn id="2" xr3:uid="{B2335CC2-CFBD-4A26-8B5A-EAD86A64E596}" name="Training Duration"/>
+    <tableColumn id="3" xr3:uid="{C4D378BC-CE64-4DE2-96B7-F774912DB114}" name="Nr Of Points" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{46C5C1CB-C5F4-4A2F-97E4-599F697072D4}" name="Resolution"/>
+    <tableColumn id="5" xr3:uid="{D44FCDD2-ACCD-423D-9562-37EB6C1F0B2B}" name="PSNR (Start)"/>
+    <tableColumn id="6" xr3:uid="{3DE463D2-E1A1-4BE7-8B3C-F08BD0660649}" name="PSNR (End)"/>
+    <tableColumn id="7" xr3:uid="{8C1A1A61-B08F-4F0D-BD86-CC69AE3B1D0A}" name="Loss (Start)"/>
+    <tableColumn id="8" xr3:uid="{7A76DC0F-06AE-4978-B8E6-DF8BEA3B0189}" name="Loss (End)"/>
+    <tableColumn id="9" xr3:uid="{222F5043-C77F-432A-BD58-ABA845CCCB6B}" name="Nr of Points End"/>
+    <tableColumn id="10" xr3:uid="{7153EC0E-F51D-491E-82A9-2DBB8F904443}" name="Comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F0B7A215-271E-49DA-A4A7-9FCBFF5A1EDA}" name="Tabelle37" displayName="Tabelle37" ref="O48:Q50" totalsRowShown="0">
+  <autoFilter ref="O48:Q50" xr:uid="{F0B7A215-271E-49DA-A4A7-9FCBFF5A1EDA}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EA30E107-D9F6-41DA-A593-91735E1F82A2}" name="Spalte1"/>
+    <tableColumn id="2" xr3:uid="{6D3D17D9-B406-48F7-AC78-669CE14997B9}" name="Blue" dataDxfId="1" dataCellStyle="Prozent">
+      <calculatedColumnFormula>(46*60+6)/(52*60+17)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{462D7421-1A6B-471C-B1FC-F03FC01A8B74}" name="Red" dataDxfId="0" dataCellStyle="Prozent">
+      <calculatedColumnFormula>M53/M52</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -574,27 +2756,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C03B34-FF9A-4BAB-BFFD-D449B574B7AC}">
-  <dimension ref="C5:K40"/>
+  <dimension ref="C3:X81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:24" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="C3" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -606,24 +2818,51 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
         <v>8</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>9</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="S7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>0.23958333333333334</v>
@@ -631,8 +2870,8 @@
       <c r="E8">
         <v>100000</v>
       </c>
-      <c r="F8" t="s">
-        <v>3</v>
+      <c r="F8" s="20">
+        <v>0.5</v>
       </c>
       <c r="G8" s="4">
         <v>26.5</v>
@@ -646,13 +2885,40 @@
       <c r="J8">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>25.88</v>
+      </c>
+      <c r="R8" s="25">
+        <v>30.01</v>
+      </c>
+      <c r="S8" s="25">
+        <v>32210</v>
+      </c>
+      <c r="T8" s="26">
+        <f>6*60+19</f>
+        <v>379</v>
+      </c>
+      <c r="V8" t="s">
+        <v>38</v>
+      </c>
+      <c r="W8" s="36">
+        <f>R9/R8</f>
+        <v>1.1529490169943353</v>
+      </c>
+      <c r="X8" s="35">
+        <f>R11/R10</f>
+        <v>1.0269461077844313</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1">
         <v>0.23611111111111113</v>
@@ -660,8 +2926,8 @@
       <c r="E9">
         <v>100000</v>
       </c>
-      <c r="F9" t="s">
-        <v>3</v>
+      <c r="F9" s="20">
+        <v>0.5</v>
       </c>
       <c r="G9">
         <v>26.65</v>
@@ -675,113 +2941,257 @@
       <c r="J9">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>30.29</v>
+      </c>
+      <c r="R9" s="25">
+        <v>34.6</v>
+      </c>
+      <c r="S9" s="16">
+        <v>53422</v>
+      </c>
+      <c r="T9" s="26">
+        <f>5*60+7</f>
+        <v>307</v>
+      </c>
+      <c r="V9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" s="36">
+        <f t="shared" ref="W9" si="0">R10/R9</f>
+        <v>0.86878612716763004</v>
+      </c>
+      <c r="X9" s="35">
+        <f>T11/T10</f>
+        <v>0.85036119711042313</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0.21319444444444444</v>
+      </c>
+      <c r="E10" s="13">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="13">
+        <v>30.29</v>
+      </c>
+      <c r="H10" s="13">
+        <v>34.6</v>
+      </c>
+      <c r="I10" s="13">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J10" s="13">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="K10" s="13">
+        <v>53422</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="P10" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>27.31</v>
+      </c>
+      <c r="R10" s="32">
+        <v>30.06</v>
+      </c>
+      <c r="S10" s="27"/>
+      <c r="T10" s="31">
+        <f>16*60+9</f>
+        <v>969</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="14">
         <v>0.21319444444444444</v>
       </c>
-      <c r="E10">
+      <c r="E11" s="13">
         <v>100000</v>
       </c>
-      <c r="F10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10">
-        <v>30.29</v>
-      </c>
-      <c r="H10">
-        <v>34.6</v>
-      </c>
-      <c r="I10">
+      <c r="F11" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="13">
+        <v>30.35</v>
+      </c>
+      <c r="H11" s="13">
+        <v>35.1</v>
+      </c>
+      <c r="I11" s="13">
         <v>1.2E-2</v>
       </c>
-      <c r="J10">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="J11" s="13">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="K11" s="13">
+        <v>17089</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.21319444444444444</v>
-      </c>
-      <c r="E11">
+      <c r="P11" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>27.67</v>
+      </c>
+      <c r="R11" s="32">
+        <v>30.87</v>
+      </c>
+      <c r="S11" s="32"/>
+      <c r="T11" s="30">
+        <f>13*60+44</f>
+        <v>824</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C12" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0.71180555555555547</v>
+      </c>
+      <c r="E12" s="17">
         <v>100000</v>
       </c>
-      <c r="F11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>30.35</v>
-      </c>
-      <c r="H11">
-        <v>35.1</v>
-      </c>
-      <c r="I11">
-        <v>1.2E-2</v>
-      </c>
-      <c r="J11">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F12" s="22">
+        <v>1</v>
+      </c>
+      <c r="G12" s="17">
+        <v>24.86</v>
+      </c>
+      <c r="H12" s="17">
+        <v>27.47</v>
+      </c>
+      <c r="I12" s="17">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="J12" s="17">
+        <v>1.01E-2</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="L12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C13" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="28">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="E13" s="27">
+        <v>100000</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1</v>
+      </c>
+      <c r="G13" s="27">
+        <v>27.57</v>
+      </c>
+      <c r="H13" s="27">
+        <v>30.59</v>
+      </c>
+      <c r="I13" s="27">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="J13" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="27"/>
+      <c r="L13" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C14" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="28">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="E14" s="27">
+        <v>100000</v>
+      </c>
+      <c r="F14" s="29">
+        <v>1</v>
+      </c>
+      <c r="G14" s="27">
+        <v>27.67</v>
+      </c>
+      <c r="H14" s="27">
+        <v>30.87</v>
+      </c>
+      <c r="I14" s="27">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="J14" s="27">
+        <v>1.01E-2</v>
+      </c>
+      <c r="K14" s="27"/>
+      <c r="L14" s="30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="E15" s="1"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="E16" s="1"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E17" s="1"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E18" s="1"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E19" s="1"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E20" s="1"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E21" s="1"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="12"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
         <v>1</v>
@@ -793,24 +3203,27 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" t="s">
         <v>8</v>
       </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>9</v>
       </c>
-      <c r="J26" t="s">
-        <v>10</v>
-      </c>
       <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D27" s="1">
         <v>0.19999999999999998</v>
@@ -818,8 +3231,8 @@
       <c r="E27" s="4">
         <v>100000</v>
       </c>
-      <c r="F27" t="s">
-        <v>3</v>
+      <c r="F27" s="20">
+        <v>0.5</v>
       </c>
       <c r="G27">
         <v>26.81</v>
@@ -833,81 +3246,467 @@
       <c r="J27">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0.26319444444444445</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F28" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="13">
+        <v>25.88</v>
+      </c>
+      <c r="H28" s="13">
+        <v>30.01</v>
+      </c>
+      <c r="I28" s="13">
+        <v>1.47E-2</v>
+      </c>
+      <c r="J28" s="13">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="K28" s="13">
+        <v>32210</v>
+      </c>
+      <c r="L28" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.26319444444444445</v>
-      </c>
-      <c r="E28" s="4">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="18">
+        <v>0.81736111111111109</v>
+      </c>
+      <c r="E29" s="19">
         <v>100000</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" s="22">
+        <v>1</v>
+      </c>
+      <c r="G29" s="17">
+        <v>24.6</v>
+      </c>
+      <c r="H29" s="17">
+        <v>28.1</v>
+      </c>
+      <c r="I29" s="17">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J29" s="17">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="28">
+        <v>0.67291666666666661</v>
+      </c>
+      <c r="E30" s="31">
+        <v>100000</v>
+      </c>
+      <c r="F30" s="29">
+        <v>1</v>
+      </c>
+      <c r="G30" s="27">
+        <v>27.31</v>
+      </c>
+      <c r="H30" s="27">
+        <v>30.06</v>
+      </c>
+      <c r="I30" s="27">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="J30" s="27">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="43" spans="3:17" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="C43" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+    </row>
+    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C46" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G28">
-        <v>25.88</v>
-      </c>
-      <c r="H28">
-        <v>30.01</v>
-      </c>
-      <c r="I28">
-        <v>1.47E-2</v>
-      </c>
-      <c r="J28">
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="P46" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="1"/>
+      <c r="D48" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" t="s">
+        <v>20</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" t="s">
+        <v>42</v>
+      </c>
+      <c r="P48" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q48" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C49" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="45">
+        <v>1.9208333333333334</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="21">
+        <v>1</v>
+      </c>
+      <c r="G49" s="15">
+        <v>32.6</v>
+      </c>
+      <c r="H49" s="13">
+        <v>30.19</v>
+      </c>
+      <c r="I49" s="13">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J49" s="13">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="K49" s="13"/>
+      <c r="L49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" s="36">
+        <f>Tabelle15[[#This Row],[PSNR (End)]]/H68</f>
+        <v>1.3194930069930071</v>
+      </c>
+      <c r="Q49" s="35"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C50" s="40"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="37"/>
+      <c r="O50" t="s">
+        <v>39</v>
+      </c>
+      <c r="P50" s="36">
+        <f t="shared" ref="P50" si="1">(46*60+6)/(52*60+17)</f>
+        <v>0.88173414089894808</v>
+      </c>
+      <c r="Q50" s="35"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C51" s="40"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="37"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C52" s="40"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="37"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C53" s="40"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="37"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C54" s="40"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="37"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C55" s="40"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="37"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E56" s="1"/>
+      <c r="L56" s="10"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E57" s="1"/>
+      <c r="L57" s="10"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E58" s="1"/>
+      <c r="L58" s="10"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E59" s="1"/>
+      <c r="L59" s="10"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E60" s="1"/>
+      <c r="L60" s="10"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E61" s="1"/>
+      <c r="L61" s="10"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E62" s="1"/>
+      <c r="L62" s="12"/>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" t="s">
+        <v>10</v>
+      </c>
+      <c r="I67" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K67" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C68" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="45">
+        <v>2.1784722222222221</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F68" s="21">
+        <v>1</v>
+      </c>
+      <c r="G68" s="13">
+        <v>23.28</v>
+      </c>
+      <c r="H68" s="13">
+        <v>22.88</v>
+      </c>
+      <c r="I68" s="13">
+        <v>0.1051</v>
+      </c>
+      <c r="J68" s="13">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+    </row>
+    <row r="69" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E69" s="1"/>
+      <c r="K69" s="40"/>
+      <c r="L69" s="40"/>
+    </row>
+    <row r="70" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C70" s="40"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
+      <c r="L70" s="40"/>
+    </row>
+    <row r="71" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C71" s="40"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="40"/>
+    </row>
+    <row r="72" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E74" s="1"/>
+    </row>
+    <row r="75" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E75" s="1"/>
+    </row>
+    <row r="76" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E76" s="1"/>
+    </row>
+    <row r="77" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E77" s="1"/>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E78" s="1"/>
+    </row>
+    <row r="79" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E79" s="1"/>
+    </row>
+    <row r="80" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E80" s="1"/>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="6">
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Timings.xlsx
+++ b/Timings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\TESTS\gs\avis-gaussian-splatting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723323E2-75A2-4090-AD74-D10E792BDEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6605080F-B9B3-44EA-B40E-E0D76931058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5805" yWindow="1500" windowWidth="35625" windowHeight="17385" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
+    <workbookView xWindow="10545" yWindow="8790" windowWidth="38700" windowHeight="15345" xr2:uid="{91218539-CA6E-4D46-9F47-0C4D7F2F2CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
   <si>
     <t>Nr Of Points</t>
   </si>
@@ -186,6 +186,21 @@
   </si>
   <si>
     <t>Ohne Rotation &amp; Scaling!</t>
+  </si>
+  <si>
+    <t>Verbesserung</t>
+  </si>
+  <si>
+    <t>SfM Initialization</t>
+  </si>
+  <si>
+    <t>Only 19 cams</t>
+  </si>
+  <si>
+    <t>99 Cams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ac79d7eb-4 </t>
   </si>
 </sst>
 </file>
@@ -195,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,8 +250,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,6 +293,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,7 +360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -378,12 +407,24 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -438,55 +479,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
@@ -2261,15 +2253,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>128586</xdr:rowOff>
+      <xdr:colOff>400049</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2298,14 +2290,14 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>461962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>252412</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2339,7 +2331,7 @@
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EA3F6830-BAC4-4FD9-A394-9E999F8033CE}" name="Code"/>
     <tableColumn id="2" xr3:uid="{F091966C-55EF-48D3-B415-C56E9FE9AAC5}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Nr Of Points" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{4C1CFC3C-F530-4FFA-A8CA-ADF991176FFD}" name="Nr Of Points" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{E9B572CD-3E9A-4CEA-9B7C-305488712FFB}" name="Resolution"/>
     <tableColumn id="6" xr3:uid="{94FB43B6-19FB-4A94-A78E-1026CB6E37F2}" name="PSNR (Start)"/>
     <tableColumn id="7" xr3:uid="{18CF464E-7E9E-4DB2-BCF0-CFB02527AC18}" name="PSNR (End)"/>
@@ -2352,12 +2344,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}" name="Tabelle13" displayName="Tabelle13" ref="C26:L40" totalsRowShown="0">
-  <autoFilter ref="C26:L40" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}" name="Tabelle13" displayName="Tabelle13" ref="C26:L33" totalsRowShown="0">
+  <autoFilter ref="C26:L33" xr:uid="{41A20CA5-4675-49BB-8958-E2F68EA96ED0}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5ADD7675-23D6-40D9-8031-52023CB23480}" name="Code"/>
     <tableColumn id="2" xr3:uid="{14203E69-6608-483D-BBEB-EB038E259A23}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{5FE5403A-FE12-41A1-BE7D-0FC20267D7C4}" name="Nr Of Points" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5FE5403A-FE12-41A1-BE7D-0FC20267D7C4}" name="Nr Of Points" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{6BB98B40-3C2F-4659-B95E-6F199432AF52}" name="Resolution"/>
     <tableColumn id="5" xr3:uid="{B4B69CDA-51CC-4214-89F5-CD30E8EB4931}" name="PSNR (Start)"/>
     <tableColumn id="6" xr3:uid="{C2AAF3AF-1964-4907-9B53-4AAEF160B32B}" name="PSNR (End)"/>
@@ -2371,28 +2363,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CAF6CA38-A879-4E1D-939A-4F49F01E476B}" name="Tabelle3" displayName="Tabelle3" ref="V7:X9" totalsRowShown="0">
-  <autoFilter ref="V7:X9" xr:uid="{CAF6CA38-A879-4E1D-939A-4F49F01E476B}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{ADF7F475-D563-4612-8AD8-71DAD1D2CE7C}" name="Spalte1"/>
-    <tableColumn id="2" xr3:uid="{8EE6E213-7A6E-49E0-8C89-CA05EE60D19B}" name="Blue" dataDxfId="5" dataCellStyle="Prozent">
-      <calculatedColumnFormula>R9/R8</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{696629D8-E2FE-486F-8554-54A0C09074BE}" name="Red" dataDxfId="4" dataCellStyle="Prozent">
-      <calculatedColumnFormula>T10/T9</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24567F50-1684-4737-947B-346844D16070}" name="Tabelle15" displayName="Tabelle15" ref="C48:K62" totalsRowShown="0">
-  <autoFilter ref="C48:K62" xr:uid="{24567F50-1684-4737-947B-346844D16070}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24567F50-1684-4737-947B-346844D16070}" name="Tabelle15" displayName="Tabelle15" ref="C53:K67" totalsRowShown="0">
+  <autoFilter ref="C53:K67" xr:uid="{24567F50-1684-4737-947B-346844D16070}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{16B84E3B-6F04-4493-8D97-29CD2344449A}" name="Code"/>
     <tableColumn id="2" xr3:uid="{610A843A-B98C-47B1-A6D3-CDB811A53CE8}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{DF755203-AFBC-4860-BD4F-4432648FEE7D}" name="Nr Of Points" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{DF755203-AFBC-4860-BD4F-4432648FEE7D}" name="Nr Of Points" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{9547ACFC-FF01-4E72-884B-AF7F5B534A68}" name="Resolution"/>
     <tableColumn id="6" xr3:uid="{F05F4F04-CECB-4BD0-9A43-9A1B85591A96}" name="PSNR (Start)"/>
     <tableColumn id="7" xr3:uid="{B62AC83F-DE2B-468B-B129-6BD01F2C00B2}" name="PSNR (End)"/>
@@ -2404,13 +2380,13 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}" name="Tabelle136" displayName="Tabelle136" ref="C67:L81" totalsRowShown="0">
-  <autoFilter ref="C67:L81" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}"/>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}" name="Tabelle136" displayName="Tabelle136" ref="C72:L86" totalsRowShown="0">
+  <autoFilter ref="C72:L86" xr:uid="{2C8F774A-F8A0-4009-BB08-95183D210C6A}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{42E5749D-01BF-4157-AA2C-7D3D72631E67}" name="Code"/>
     <tableColumn id="2" xr3:uid="{B2335CC2-CFBD-4A26-8B5A-EAD86A64E596}" name="Training Duration"/>
-    <tableColumn id="3" xr3:uid="{C4D378BC-CE64-4DE2-96B7-F774912DB114}" name="Nr Of Points" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{C4D378BC-CE64-4DE2-96B7-F774912DB114}" name="Nr Of Points" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{46C5C1CB-C5F4-4A2F-97E4-599F697072D4}" name="Resolution"/>
     <tableColumn id="5" xr3:uid="{D44FCDD2-ACCD-423D-9562-37EB6C1F0B2B}" name="PSNR (Start)"/>
     <tableColumn id="6" xr3:uid="{3DE463D2-E1A1-4BE7-8B3C-F08BD0660649}" name="PSNR (End)"/>
@@ -2423,17 +2399,36 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F0B7A215-271E-49DA-A4A7-9FCBFF5A1EDA}" name="Tabelle37" displayName="Tabelle37" ref="O48:Q50" totalsRowShown="0">
   <autoFilter ref="O48:Q50" xr:uid="{F0B7A215-271E-49DA-A4A7-9FCBFF5A1EDA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EA30E107-D9F6-41DA-A593-91735E1F82A2}" name="Spalte1"/>
-    <tableColumn id="2" xr3:uid="{6D3D17D9-B406-48F7-AC78-669CE14997B9}" name="Blue" dataDxfId="1" dataCellStyle="Prozent">
+    <tableColumn id="2" xr3:uid="{6D3D17D9-B406-48F7-AC78-669CE14997B9}" name="Blue" dataDxfId="2" dataCellStyle="Prozent">
       <calculatedColumnFormula>(46*60+6)/(52*60+17)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{462D7421-1A6B-471C-B1FC-F03FC01A8B74}" name="Red" dataDxfId="0" dataCellStyle="Prozent">
+    <tableColumn id="3" xr3:uid="{462D7421-1A6B-471C-B1FC-F03FC01A8B74}" name="Red" dataDxfId="1" dataCellStyle="Prozent">
       <calculatedColumnFormula>M53/M52</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{552798EA-6E25-4DE9-B62B-D96EA9F67CE9}" name="Tabelle134" displayName="Tabelle134" ref="C37:L44" totalsRowShown="0">
+  <autoFilter ref="C37:L44" xr:uid="{552798EA-6E25-4DE9-B62B-D96EA9F67CE9}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{318E4B5C-909D-460D-9809-78F39ABB233F}" name="Code"/>
+    <tableColumn id="2" xr3:uid="{01D62633-3733-4B27-B4F3-4A92A3D8FB83}" name="Training Duration"/>
+    <tableColumn id="3" xr3:uid="{1662019F-FBDC-41A6-87DE-11C9125A93A1}" name="Nr Of Points" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{D2E104B1-D5C9-4F5C-88E6-D4445D6DA7A0}" name="Resolution"/>
+    <tableColumn id="5" xr3:uid="{B870C93C-2775-4D1E-8E69-5C40ED5881D5}" name="PSNR (Start)"/>
+    <tableColumn id="6" xr3:uid="{C4375F16-243B-47DA-BC95-30B3A0D8D1D4}" name="PSNR (End)"/>
+    <tableColumn id="7" xr3:uid="{0C17EB1A-5A28-4E8C-8EC6-A11A2FAF2A1C}" name="Loss (Start)"/>
+    <tableColumn id="8" xr3:uid="{D0CF387A-DFB9-4E71-B870-98CD59BC9DCA}" name="Loss (End)"/>
+    <tableColumn id="9" xr3:uid="{DAB44917-5346-40ED-AEB7-85ED8D21108F}" name="Nr of Points End"/>
+    <tableColumn id="10" xr3:uid="{B38E8610-EC65-4FEE-B08D-14A086D12921}" name="Comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2756,7 +2751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C03B34-FF9A-4BAB-BFFD-D449B574B7AC}">
-  <dimension ref="C3:X81"/>
+  <dimension ref="C3:T86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
@@ -2769,10 +2764,9 @@
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:24" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="C3" s="39" t="s">
         <v>44</v>
       </c>
@@ -2785,7 +2779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.25">
       <c r="G4" t="s">
         <v>33</v>
       </c>
@@ -2793,18 +2787,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -2850,17 +2841,8 @@
       <c r="T7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="V7" t="s">
-        <v>42</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="X7" s="34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
@@ -2904,19 +2886,8 @@
         <f>6*60+19</f>
         <v>379</v>
       </c>
-      <c r="V8" t="s">
-        <v>38</v>
-      </c>
-      <c r="W8" s="36">
-        <f>R9/R8</f>
-        <v>1.1529490169943353</v>
-      </c>
-      <c r="X8" s="35">
-        <f>R11/R10</f>
-        <v>1.0269461077844313</v>
-      </c>
-    </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>6</v>
       </c>
@@ -2960,19 +2931,8 @@
         <f>5*60+7</f>
         <v>307</v>
       </c>
-      <c r="V9" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9" s="36">
-        <f t="shared" ref="W9" si="0">R10/R9</f>
-        <v>0.86878612716763004</v>
-      </c>
-      <c r="X9" s="35">
-        <f>T11/T10</f>
-        <v>0.85036119711042313</v>
-      </c>
-    </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
@@ -3018,7 +2978,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
@@ -3064,7 +3024,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C12" s="17" t="s">
         <v>29</v>
       </c>
@@ -3095,7 +3055,7 @@
       </c>
       <c r="P12" s="11"/>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C13" s="27" t="s">
         <v>31</v>
       </c>
@@ -3124,9 +3084,8 @@
       <c r="L13" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C14" s="27" t="s">
         <v>35</v>
       </c>
@@ -3155,14 +3114,94 @@
       <c r="L14" s="30" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="E15" s="1"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="E16" s="1"/>
-      <c r="L16" s="10"/>
+      <c r="O14" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="47">
+        <f>Q9/Q8</f>
+        <v>1.1704018547140649</v>
+      </c>
+      <c r="R14" s="47">
+        <f>R9/R8</f>
+        <v>1.1529490169943353</v>
+      </c>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47">
+        <f>1-T9/T8</f>
+        <v>0.18997361477572561</v>
+      </c>
+    </row>
+    <row r="15" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C15" s="50"/>
+      <c r="D15" s="51">
+        <v>0.21458333333333335</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="50">
+        <v>27.8</v>
+      </c>
+      <c r="H15" s="50">
+        <v>31.35</v>
+      </c>
+      <c r="I15" s="50">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J15" s="50">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="K15" s="50"/>
+      <c r="L15" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="49">
+        <f>Q11/Q10</f>
+        <v>1.0131819846210182</v>
+      </c>
+      <c r="R15" s="49">
+        <f>R11/R10</f>
+        <v>1.0269461077844313</v>
+      </c>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49">
+        <f>1-T11/T10</f>
+        <v>0.14963880288957687</v>
+      </c>
+    </row>
+    <row r="16" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="E16" s="4">
+        <v>7906</v>
+      </c>
+      <c r="F16" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="G16">
+        <v>26.57</v>
+      </c>
+      <c r="H16">
+        <v>30.53</v>
+      </c>
+      <c r="I16">
+        <v>1.17E-2</v>
+      </c>
+      <c r="J16">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E17" s="1"/>
@@ -3349,73 +3388,153 @@
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E34" s="1"/>
-    </row>
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E36" s="1"/>
+      <c r="C35" s="5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E37" s="1"/>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="20"/>
     </row>
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E39" s="1"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E40" s="1"/>
-    </row>
-    <row r="43" spans="3:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C43" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+    </row>
+    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C41" s="27"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+    </row>
+    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C42" s="50"/>
+      <c r="D42" s="51">
+        <v>0.18958333333333333</v>
+      </c>
+      <c r="E42" s="54">
+        <v>650</v>
+      </c>
+      <c r="F42" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="50">
+        <v>42.61</v>
+      </c>
+      <c r="H42" s="50">
+        <v>44.93</v>
+      </c>
+      <c r="I42" s="50">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="J42" s="50">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K42" s="50"/>
+      <c r="L42" s="50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="D43" s="1">
+        <v>0.21041666666666667</v>
+      </c>
+      <c r="E43" s="4">
+        <v>7906</v>
+      </c>
+      <c r="F43" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="G43">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="H43">
+        <v>43.73</v>
+      </c>
+      <c r="I43">
+        <v>2.8E-3</v>
+      </c>
+      <c r="J43">
+        <v>1.5E-3</v>
+      </c>
+      <c r="L43" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E44" s="1"/>
     </row>
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C46" s="6" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>0</v>
-      </c>
-      <c r="F48" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" t="s">
-        <v>9</v>
-      </c>
-      <c r="K48" t="s">
-        <v>20</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>5</v>
-      </c>
+    <row r="48" spans="3:17" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="C48" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
       <c r="O48" t="s">
         <v>42</v>
       </c>
@@ -3427,110 +3546,91 @@
       </c>
     </row>
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C49" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D49" s="45">
-        <v>1.9208333333333334</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F49" s="21">
-        <v>1</v>
-      </c>
-      <c r="G49" s="15">
-        <v>32.6</v>
-      </c>
-      <c r="H49" s="13">
-        <v>30.19</v>
-      </c>
-      <c r="I49" s="13">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="J49" s="13">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K49" s="13"/>
-      <c r="L49" s="16" t="s">
-        <v>49</v>
-      </c>
       <c r="O49" t="s">
         <v>38</v>
       </c>
-      <c r="P49" s="36">
-        <f>Tabelle15[[#This Row],[PSNR (End)]]/H68</f>
-        <v>1.3194930069930071</v>
+      <c r="P49" s="36" t="e">
+        <f>Tabelle15[[#This Row],[PSNR (End)]]/H73</f>
+        <v>#VALUE!</v>
       </c>
       <c r="Q49" s="35"/>
     </row>
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C50" s="40"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="37"/>
       <c r="O50" t="s">
         <v>39</v>
       </c>
       <c r="P50" s="36">
-        <f t="shared" ref="P50" si="1">(46*60+6)/(52*60+17)</f>
+        <f>(46*60+6)/(52*60+17)</f>
         <v>0.88173414089894808</v>
       </c>
       <c r="Q50" s="35"/>
     </row>
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C51" s="40"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="37"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C52" s="40"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="37"/>
+      <c r="C51" s="6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C53" s="40"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="37"/>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C54" s="40"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="37"/>
+      <c r="C54" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" s="45">
+        <v>1.9208333333333334</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" s="21">
+        <v>1</v>
+      </c>
+      <c r="G54" s="15">
+        <v>32.6</v>
+      </c>
+      <c r="H54" s="13">
+        <v>30.19</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J54" s="13">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="K54" s="13"/>
+      <c r="L54" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="40"/>
@@ -3545,24 +3645,64 @@
       <c r="L55" s="37"/>
     </row>
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E56" s="1"/>
-      <c r="L56" s="10"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="37"/>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E57" s="1"/>
-      <c r="L57" s="10"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="37"/>
     </row>
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E58" s="1"/>
-      <c r="L58" s="10"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="37"/>
     </row>
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E59" s="1"/>
-      <c r="L59" s="10"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="37"/>
     </row>
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="E60" s="1"/>
-      <c r="L60" s="10"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="37"/>
     </row>
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E61" s="1"/>
@@ -3570,116 +3710,121 @@
     </row>
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="E62" s="1"/>
-      <c r="L62" s="12"/>
+      <c r="L62" s="10"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E63" s="1"/>
+      <c r="L63" s="10"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="E64" s="1"/>
+      <c r="L64" s="10"/>
     </row>
     <row r="65" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C65" s="5" t="s">
+      <c r="E65" s="1"/>
+      <c r="L65" s="10"/>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E66" s="1"/>
+      <c r="L66" s="10"/>
+    </row>
+    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E67" s="1"/>
+      <c r="L67" s="12"/>
+    </row>
+    <row r="70" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
+    <row r="72" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
         <v>17</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D72" t="s">
         <v>1</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E72" t="s">
         <v>0</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F72" t="s">
         <v>2</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G72" t="s">
         <v>7</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H72" t="s">
         <v>10</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I72" t="s">
         <v>8</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J72" t="s">
         <v>9</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K72" t="s">
         <v>20</v>
       </c>
-      <c r="L67" t="s">
+      <c r="L72" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C68" s="13" t="s">
+    <row r="73" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C73" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D68" s="45">
+      <c r="D73" s="45">
         <v>2.1784722222222221</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E73" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F68" s="21">
+      <c r="F73" s="21">
         <v>1</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G73" s="13">
         <v>23.28</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H73" s="13">
         <v>22.88</v>
       </c>
-      <c r="I68" s="13">
+      <c r="I73" s="13">
         <v>0.1051</v>
       </c>
-      <c r="J68" s="13">
+      <c r="J73" s="13">
         <v>4.3799999999999999E-2</v>
       </c>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-    </row>
-    <row r="69" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E69" s="1"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-    </row>
-    <row r="70" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C70" s="40"/>
-      <c r="D70" s="43"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="40"/>
-      <c r="L70" s="40"/>
-    </row>
-    <row r="71" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C71" s="40"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-      <c r="L71" s="40"/>
-    </row>
-    <row r="72" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E72" s="1"/>
-    </row>
-    <row r="73" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E73" s="1"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
     </row>
     <row r="74" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E74" s="1"/>
+      <c r="K74" s="40"/>
+      <c r="L74" s="40"/>
     </row>
     <row r="75" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E75" s="1"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
+      <c r="L75" s="40"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="E76" s="1"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="43"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
+      <c r="L76" s="40"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E77" s="1"/>
@@ -3695,6 +3840,21 @@
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E81" s="1"/>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="1"/>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="1"/>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="1"/>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="1"/>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
